--- a/fixtures/generated/tesouraria.xlsx
+++ b/fixtures/generated/tesouraria.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="238">
   <si>
     <t>Tesouraria fictícia do TUNADÃO 1998</t>
   </si>
@@ -100,384 +100,390 @@
     <t>Cartazes e impressões</t>
   </si>
   <si>
+    <t>Zumba na Caneca 2024</t>
+  </si>
+  <si>
+    <t>Comunicação e gráfica</t>
+  </si>
+  <si>
+    <t>P-003</t>
+  </si>
+  <si>
+    <t>Canecas personalizadas</t>
+  </si>
+  <si>
+    <t>Merchandising e trajes</t>
+  </si>
+  <si>
+    <t>R-002</t>
+  </si>
+  <si>
+    <t>Patrocínio ginásio local</t>
+  </si>
+  <si>
+    <t>Patrocínios</t>
+  </si>
+  <si>
+    <t>P-004</t>
+  </si>
+  <si>
+    <t>Licença de ruído e SPA</t>
+  </si>
+  <si>
+    <t>Taxas e licenças</t>
+  </si>
+  <si>
+    <t>Caixa</t>
+  </si>
+  <si>
+    <t>R-003</t>
+  </si>
+  <si>
+    <t>Apoio anual da Câmara Municipal</t>
+  </si>
+  <si>
+    <t>Subsídios e apoios</t>
+  </si>
+  <si>
+    <t>P-005</t>
+  </si>
+  <si>
+    <t>Aluguer de som</t>
+  </si>
+  <si>
+    <t>Produção (som, luz, palco)</t>
+  </si>
+  <si>
+    <t>P-006</t>
+  </si>
+  <si>
+    <t>Bebidas e consumíveis</t>
+  </si>
+  <si>
+    <t>Compras para o bar</t>
+  </si>
+  <si>
+    <t>R-004</t>
+  </si>
+  <si>
+    <t>Inscrições</t>
+  </si>
+  <si>
+    <t>Inscrições e bilheteira</t>
+  </si>
+  <si>
+    <t>R-005</t>
+  </si>
+  <si>
+    <t>Receita de bar</t>
+  </si>
+  <si>
+    <t>Bar e merchandising</t>
+  </si>
+  <si>
+    <t>T-001</t>
+  </si>
+  <si>
+    <t>Depósito do numerário do evento (saída)</t>
+  </si>
+  <si>
+    <t>Transferências internas</t>
+  </si>
+  <si>
+    <t>Depósito do numerário do evento (entrada)</t>
+  </si>
+  <si>
+    <t>R-006</t>
+  </si>
+  <si>
+    <t>Serenata para empresa</t>
+  </si>
+  <si>
+    <t>Atuações e serenatas</t>
+  </si>
+  <si>
+    <t>P-007</t>
+  </si>
+  <si>
+    <t>T-shirts do evento</t>
+  </si>
+  <si>
+    <t>18º CITADÃO</t>
+  </si>
+  <si>
+    <t>P-008</t>
+  </si>
+  <si>
+    <t>Cartazes e programa</t>
+  </si>
+  <si>
+    <t>R-007</t>
+  </si>
+  <si>
+    <t>Patrocínios do evento</t>
+  </si>
+  <si>
+    <t>R-008</t>
+  </si>
+  <si>
+    <t>Apoio anual da universidade</t>
+  </si>
+  <si>
+    <t>P-009</t>
+  </si>
+  <si>
+    <t>Licenças e SPA</t>
+  </si>
+  <si>
+    <t>P-010</t>
+  </si>
+  <si>
+    <t>Som e luz</t>
+  </si>
+  <si>
+    <t>P-011</t>
+  </si>
+  <si>
+    <t>Palco e estruturas</t>
+  </si>
+  <si>
+    <t>R-009</t>
+  </si>
+  <si>
+    <t>Inscrições das tunas</t>
+  </si>
+  <si>
+    <t>P-012</t>
+  </si>
+  <si>
+    <t>R-010</t>
+  </si>
+  <si>
+    <t>Bilheteira</t>
+  </si>
+  <si>
+    <t>R-011</t>
+  </si>
+  <si>
+    <t>Bar (TPA)</t>
+  </si>
+  <si>
+    <t>TPA</t>
+  </si>
+  <si>
+    <t>R-012</t>
+  </si>
+  <si>
+    <t>Merchandising</t>
+  </si>
+  <si>
+    <t>T-002</t>
+  </si>
+  <si>
+    <t>P-013</t>
+  </si>
+  <si>
+    <t>Refeições das tunas</t>
+  </si>
+  <si>
+    <t>Alimentação e alojamento</t>
+  </si>
+  <si>
+    <t>P-014</t>
+  </si>
+  <si>
+    <t>Alojamento</t>
+  </si>
+  <si>
+    <t>P-015</t>
+  </si>
+  <si>
+    <t>Prémios e troféus</t>
+  </si>
+  <si>
+    <t>R-013</t>
+  </si>
+  <si>
+    <t>Donativo de antigo membro</t>
+  </si>
+  <si>
+    <t>Donativos</t>
+  </si>
+  <si>
+    <t>P-016</t>
+  </si>
+  <si>
+    <t>Reparação de instrumentos</t>
+  </si>
+  <si>
+    <t>Instrumentos e manutenção</t>
+  </si>
+  <si>
+    <t>R-014</t>
+  </si>
+  <si>
+    <t>Atuação em casamento</t>
+  </si>
+  <si>
+    <t>P-017</t>
+  </si>
+  <si>
+    <t>P-018</t>
+  </si>
+  <si>
+    <t>Som do Arraial</t>
+  </si>
+  <si>
+    <t>P-019</t>
+  </si>
+  <si>
+    <t>Compras para o bar do Arraial</t>
+  </si>
+  <si>
+    <t>R-015</t>
+  </si>
+  <si>
+    <t>Bar do Arraial</t>
+  </si>
+  <si>
+    <t>P-020</t>
+  </si>
+  <si>
+    <t>Material de escritório e diversos</t>
+  </si>
+  <si>
+    <t>Outros pagamentos</t>
+  </si>
+  <si>
+    <t>R-016</t>
+  </si>
+  <si>
+    <t>Venda de material antigo</t>
+  </si>
+  <si>
+    <t>Outros recebimentos</t>
+  </si>
+  <si>
+    <t>P-021</t>
+  </si>
+  <si>
+    <t>Seguro de equipamento</t>
+  </si>
+  <si>
+    <t>Seguros e despesas bancárias</t>
+  </si>
+  <si>
+    <t>R-017</t>
+  </si>
+  <si>
+    <t>Quotas 2024 em numerário (15 membros)</t>
+  </si>
+  <si>
+    <t>P-022</t>
+  </si>
+  <si>
+    <t>Gasolina e portagens</t>
+  </si>
+  <si>
+    <t>P-023</t>
+  </si>
+  <si>
+    <t>Cordas e acessórios</t>
+  </si>
+  <si>
+    <t>R-018</t>
+  </si>
+  <si>
+    <t>Donativo em numerário</t>
+  </si>
+  <si>
+    <t>R-019</t>
+  </si>
+  <si>
+    <t>Atuação de Natal</t>
+  </si>
+  <si>
+    <t>T-003</t>
+  </si>
+  <si>
+    <t>Depósito de numerário (saída)</t>
+  </si>
+  <si>
+    <t>Depósito de numerário (entrada)</t>
+  </si>
+  <si>
+    <t>P-024</t>
+  </si>
+  <si>
+    <t>Despesas bancárias de 2024</t>
+  </si>
+  <si>
+    <t>Quotas 2025 (48 membros)</t>
+  </si>
+  <si>
+    <t>Deslocação a atuação</t>
+  </si>
+  <si>
+    <t>Zumba na Caneca 2025</t>
+  </si>
+  <si>
+    <t>Apoio da Câmara Municipal (1.ª tranche)</t>
+  </si>
+  <si>
+    <t>19º CITADÃO</t>
+  </si>
+  <si>
+    <t>Apoio da universidade (via AE ESAV)</t>
+  </si>
+  <si>
+    <t>Apoio da Junta de Freguesia</t>
+  </si>
+  <si>
+    <t>Som do Arraial (pagamento parcial)</t>
+  </si>
+  <si>
+    <t>Apoio da Junta de Freguesia ao funcionamento</t>
+  </si>
+  <si>
+    <t>Atuação em jantar de curso</t>
+  </si>
+  <si>
+    <t>Quotas 2025 em numerário (15 membros)</t>
+  </si>
+  <si>
+    <t>R-020</t>
+  </si>
+  <si>
+    <t>R-021</t>
+  </si>
+  <si>
+    <t>R-022</t>
+  </si>
+  <si>
+    <t>Despesas bancárias de 2025</t>
+  </si>
+  <si>
+    <t>Apoio da Câmara Municipal (2.ª tranche do 19º CITADÃO)</t>
+  </si>
+  <si>
+    <t>Apoio CMV</t>
+  </si>
+  <si>
+    <t>Fornecedor de som: saldo do Arraial 2025 (FT 2025/311)</t>
+  </si>
+  <si>
+    <t>Apoio da Câmara Municipal</t>
+  </si>
+  <si>
+    <t>20º CITADÃO</t>
+  </si>
+  <si>
+    <t>Apoio UPV (via AE ESAV)</t>
+  </si>
+  <si>
     <t>Zumba na Caneca</t>
   </si>
   <si>
-    <t>Comunicação e gráfica</t>
-  </si>
-  <si>
-    <t>P-003</t>
-  </si>
-  <si>
-    <t>Canecas personalizadas</t>
-  </si>
-  <si>
-    <t>Merchandising e trajes</t>
-  </si>
-  <si>
-    <t>R-002</t>
-  </si>
-  <si>
-    <t>Patrocínio ginásio local</t>
-  </si>
-  <si>
-    <t>Patrocínios</t>
-  </si>
-  <si>
-    <t>P-004</t>
-  </si>
-  <si>
-    <t>Licença de ruído e SPA</t>
-  </si>
-  <si>
-    <t>Taxas e licenças</t>
-  </si>
-  <si>
-    <t>Caixa</t>
-  </si>
-  <si>
-    <t>R-003</t>
-  </si>
-  <si>
-    <t>Apoio anual da Câmara Municipal</t>
-  </si>
-  <si>
-    <t>Subsídios e apoios</t>
-  </si>
-  <si>
-    <t>P-005</t>
-  </si>
-  <si>
-    <t>Aluguer de som</t>
-  </si>
-  <si>
-    <t>Produção (som, luz, palco)</t>
-  </si>
-  <si>
-    <t>P-006</t>
-  </si>
-  <si>
-    <t>Bebidas e consumíveis</t>
-  </si>
-  <si>
-    <t>Compras para o bar</t>
-  </si>
-  <si>
-    <t>R-004</t>
-  </si>
-  <si>
-    <t>Inscrições</t>
-  </si>
-  <si>
-    <t>Inscrições e bilheteira</t>
-  </si>
-  <si>
-    <t>R-005</t>
-  </si>
-  <si>
-    <t>Receita de bar</t>
-  </si>
-  <si>
-    <t>Bar e merchandising</t>
-  </si>
-  <si>
-    <t>T-001</t>
-  </si>
-  <si>
-    <t>Depósito do numerário do evento (saída)</t>
-  </si>
-  <si>
-    <t>Transferências internas</t>
-  </si>
-  <si>
-    <t>Depósito do numerário do evento (entrada)</t>
-  </si>
-  <si>
-    <t>R-006</t>
-  </si>
-  <si>
-    <t>Serenata para empresa</t>
-  </si>
-  <si>
-    <t>Atuações e serenatas</t>
-  </si>
-  <si>
-    <t>P-007</t>
-  </si>
-  <si>
-    <t>T-shirts do evento</t>
-  </si>
-  <si>
-    <t>18º CITADÃO</t>
-  </si>
-  <si>
-    <t>P-008</t>
-  </si>
-  <si>
-    <t>Cartazes e programa</t>
-  </si>
-  <si>
-    <t>R-007</t>
-  </si>
-  <si>
-    <t>Patrocínios do evento</t>
-  </si>
-  <si>
-    <t>R-008</t>
-  </si>
-  <si>
-    <t>Apoio anual da universidade</t>
-  </si>
-  <si>
-    <t>P-009</t>
-  </si>
-  <si>
-    <t>Licenças e SPA</t>
-  </si>
-  <si>
-    <t>P-010</t>
-  </si>
-  <si>
-    <t>Som e luz</t>
-  </si>
-  <si>
-    <t>P-011</t>
-  </si>
-  <si>
-    <t>Palco e estruturas</t>
-  </si>
-  <si>
-    <t>R-009</t>
-  </si>
-  <si>
-    <t>Inscrições das tunas</t>
-  </si>
-  <si>
-    <t>P-012</t>
-  </si>
-  <si>
-    <t>R-010</t>
-  </si>
-  <si>
-    <t>Bilheteira</t>
-  </si>
-  <si>
-    <t>R-011</t>
-  </si>
-  <si>
-    <t>Bar (TPA)</t>
-  </si>
-  <si>
-    <t>TPA</t>
-  </si>
-  <si>
-    <t>R-012</t>
-  </si>
-  <si>
-    <t>Merchandising</t>
-  </si>
-  <si>
-    <t>T-002</t>
-  </si>
-  <si>
-    <t>P-013</t>
-  </si>
-  <si>
-    <t>Refeições das tunas</t>
-  </si>
-  <si>
-    <t>Alimentação e alojamento</t>
-  </si>
-  <si>
-    <t>P-014</t>
-  </si>
-  <si>
-    <t>Alojamento</t>
-  </si>
-  <si>
-    <t>P-015</t>
-  </si>
-  <si>
-    <t>Prémios e troféus</t>
-  </si>
-  <si>
-    <t>R-013</t>
-  </si>
-  <si>
-    <t>Donativo de antigo membro</t>
-  </si>
-  <si>
-    <t>Donativos</t>
-  </si>
-  <si>
-    <t>P-016</t>
-  </si>
-  <si>
-    <t>Reparação de instrumentos</t>
-  </si>
-  <si>
-    <t>Instrumentos e manutenção</t>
-  </si>
-  <si>
-    <t>R-014</t>
-  </si>
-  <si>
-    <t>Atuação em casamento</t>
-  </si>
-  <si>
-    <t>P-017</t>
-  </si>
-  <si>
-    <t>P-018</t>
-  </si>
-  <si>
-    <t>Som do Arraial</t>
-  </si>
-  <si>
-    <t>P-019</t>
-  </si>
-  <si>
-    <t>Compras para o bar do Arraial</t>
-  </si>
-  <si>
-    <t>R-015</t>
-  </si>
-  <si>
-    <t>Bar do Arraial</t>
-  </si>
-  <si>
-    <t>P-020</t>
-  </si>
-  <si>
-    <t>Material de escritório e diversos</t>
-  </si>
-  <si>
-    <t>Outros pagamentos</t>
-  </si>
-  <si>
-    <t>R-016</t>
-  </si>
-  <si>
-    <t>Venda de material antigo</t>
-  </si>
-  <si>
-    <t>Outros recebimentos</t>
-  </si>
-  <si>
-    <t>P-021</t>
-  </si>
-  <si>
-    <t>Seguro de equipamento</t>
-  </si>
-  <si>
-    <t>Seguros e despesas bancárias</t>
-  </si>
-  <si>
-    <t>R-017</t>
-  </si>
-  <si>
-    <t>Quotas 2024 em numerário (15 membros)</t>
-  </si>
-  <si>
-    <t>P-022</t>
-  </si>
-  <si>
-    <t>Gasolina e portagens</t>
-  </si>
-  <si>
-    <t>P-023</t>
-  </si>
-  <si>
-    <t>Cordas e acessórios</t>
-  </si>
-  <si>
-    <t>R-018</t>
-  </si>
-  <si>
-    <t>Donativo em numerário</t>
-  </si>
-  <si>
-    <t>R-019</t>
-  </si>
-  <si>
-    <t>Atuação de Natal</t>
-  </si>
-  <si>
-    <t>T-003</t>
-  </si>
-  <si>
-    <t>Depósito de numerário (saída)</t>
-  </si>
-  <si>
-    <t>Depósito de numerário (entrada)</t>
-  </si>
-  <si>
-    <t>P-024</t>
-  </si>
-  <si>
-    <t>Despesas bancárias de 2024</t>
-  </si>
-  <si>
-    <t>Quotas 2025 (48 membros)</t>
-  </si>
-  <si>
-    <t>Deslocação a atuação</t>
-  </si>
-  <si>
-    <t>Apoio da Câmara Municipal (1.ª tranche)</t>
-  </si>
-  <si>
-    <t>19º CITADÃO</t>
-  </si>
-  <si>
-    <t>Apoio da universidade (via AE ESAV)</t>
-  </si>
-  <si>
-    <t>Apoio da Junta de Freguesia</t>
-  </si>
-  <si>
-    <t>Som do Arraial (pagamento parcial)</t>
-  </si>
-  <si>
-    <t>Apoio da Junta de Freguesia ao funcionamento</t>
-  </si>
-  <si>
-    <t>Atuação em jantar de curso</t>
-  </si>
-  <si>
-    <t>Quotas 2025 em numerário (15 membros)</t>
-  </si>
-  <si>
-    <t>R-020</t>
-  </si>
-  <si>
-    <t>R-021</t>
-  </si>
-  <si>
-    <t>R-022</t>
-  </si>
-  <si>
-    <t>Despesas bancárias de 2025</t>
-  </si>
-  <si>
-    <t>Apoio da Câmara Municipal (2.ª tranche do 19º CITADÃO)</t>
-  </si>
-  <si>
-    <t>Apoio CMV</t>
-  </si>
-  <si>
-    <t>Fornecedor de som: saldo do Arraial 2025 (FT 2025/311)</t>
-  </si>
-  <si>
-    <t>Apoio da Câmara Municipal</t>
-  </si>
-  <si>
-    <t>20º CITADÃO</t>
-  </si>
-  <si>
-    <t>Apoio UPV</t>
-  </si>
-  <si>
     <t>Canecas personalizadas (300 un.)</t>
   </si>
   <si>
@@ -520,7 +526,7 @@
     <t>Quotas 2026 em numerário (17 membros)</t>
   </si>
   <si>
-    <t>Apoio Junta</t>
+    <t>Apoio Junta de Freguesia</t>
   </si>
   <si>
     <t>Bilheteira (TPA)</t>
@@ -559,7 +565,7 @@
     <t>Quotas recebidas (6 membros, regularização)</t>
   </si>
   <si>
-    <t>Atuação: receção ao caloiro</t>
+    <t>Atuação · receção ao caloiro</t>
   </si>
   <si>
     <t>P-028</t>
@@ -3186,7 +3192,7 @@
         <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E54" t="s">
         <v>31</v>
@@ -3224,7 +3230,7 @@
         <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -3262,7 +3268,7 @@
         <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E56" t="s">
         <v>34</v>
@@ -3300,7 +3306,7 @@
         <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E57" t="s">
         <v>37</v>
@@ -3338,7 +3344,7 @@
         <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
@@ -3376,7 +3382,7 @@
         <v>43</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E59" t="s">
         <v>44</v>
@@ -3411,10 +3417,10 @@
         <v>48</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E60" t="s">
         <v>41</v>
@@ -3452,7 +3458,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E61" t="s">
         <v>50</v>
@@ -3490,7 +3496,7 @@
         <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
         <v>53</v>
@@ -3528,7 +3534,7 @@
         <v>55</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
         <v>56</v>
@@ -3566,7 +3572,7 @@
         <v>57</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s">
         <v>56</v>
@@ -3604,7 +3610,7 @@
         <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
         <v>31</v>
@@ -3642,7 +3648,7 @@
         <v>67</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E66" t="s">
         <v>34</v>
@@ -3680,7 +3686,7 @@
         <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -3715,10 +3721,10 @@
         <v>68</v>
       </c>
       <c r="C68" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" t="s">
         <v>137</v>
-      </c>
-      <c r="D68" t="s">
-        <v>136</v>
       </c>
       <c r="E68" t="s">
         <v>41</v>
@@ -3753,10 +3759,10 @@
         <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D69" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E69" t="s">
         <v>41</v>
@@ -3794,7 +3800,7 @@
         <v>71</v>
       </c>
       <c r="D70" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E70" t="s">
         <v>37</v>
@@ -3832,7 +3838,7 @@
         <v>73</v>
       </c>
       <c r="D71" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E71" t="s">
         <v>44</v>
@@ -3870,7 +3876,7 @@
         <v>75</v>
       </c>
       <c r="D72" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E72" t="s">
         <v>44</v>
@@ -3908,7 +3914,7 @@
         <v>77</v>
       </c>
       <c r="D73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E73" t="s">
         <v>50</v>
@@ -3946,7 +3952,7 @@
         <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E74" t="s">
         <v>47</v>
@@ -3984,7 +3990,7 @@
         <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E75" t="s">
         <v>50</v>
@@ -4022,7 +4028,7 @@
         <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E76" t="s">
         <v>53</v>
@@ -4060,7 +4066,7 @@
         <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E77" t="s">
         <v>53</v>
@@ -4098,7 +4104,7 @@
         <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E78" t="s">
         <v>56</v>
@@ -4136,7 +4142,7 @@
         <v>57</v>
       </c>
       <c r="D79" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E79" t="s">
         <v>56</v>
@@ -4174,7 +4180,7 @@
         <v>88</v>
       </c>
       <c r="D80" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E80" t="s">
         <v>89</v>
@@ -4212,7 +4218,7 @@
         <v>91</v>
       </c>
       <c r="D81" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E81" t="s">
         <v>89</v>
@@ -4250,7 +4256,7 @@
         <v>93</v>
       </c>
       <c r="D82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E82" t="s">
         <v>93</v>
@@ -4513,7 +4519,7 @@
         <v>105</v>
       </c>
       <c r="C89" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -4589,7 +4595,7 @@
         <v>118</v>
       </c>
       <c r="C91" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
@@ -4627,7 +4633,7 @@
         <v>124</v>
       </c>
       <c r="C92" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D92" t="s">
         <v>16</v>
@@ -4703,7 +4709,7 @@
         <v>126</v>
       </c>
       <c r="C94" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D94" t="s">
         <v>16</v>
@@ -4738,7 +4744,7 @@
         <v>45947</v>
       </c>
       <c r="B95" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
         <v>113</v>
@@ -4852,7 +4858,7 @@
         <v>45976</v>
       </c>
       <c r="B98" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C98" t="s">
         <v>127</v>
@@ -4890,7 +4896,7 @@
         <v>45993</v>
       </c>
       <c r="B99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C99" t="s">
         <v>125</v>
@@ -5007,7 +5013,7 @@
         <v>131</v>
       </c>
       <c r="C102" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D102" t="s">
         <v>16</v>
@@ -5045,7 +5051,7 @@
         <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D103" t="s">
         <v>16</v>
@@ -5054,7 +5060,7 @@
         <v>41</v>
       </c>
       <c r="F103" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G103" t="s">
         <v>18</v>
@@ -5086,7 +5092,7 @@
         <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D104" t="s">
         <v>22</v>
@@ -5127,16 +5133,16 @@
         <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D105" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E105" t="s">
         <v>41</v>
       </c>
       <c r="F105" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G105" t="s">
         <v>18</v>
@@ -5171,7 +5177,7 @@
         <v>65</v>
       </c>
       <c r="D106" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5206,16 +5212,16 @@
         <v>39</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E107" t="s">
         <v>41</v>
       </c>
       <c r="F107" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G107" t="s">
         <v>18</v>
@@ -5250,7 +5256,7 @@
         <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5288,10 +5294,10 @@
         <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D109" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E109" t="s">
         <v>31</v>
@@ -5329,13 +5335,13 @@
         <v>33</v>
       </c>
       <c r="D110" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E110" t="s">
         <v>34</v>
       </c>
       <c r="F110" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G110" t="s">
         <v>18</v>
@@ -5370,7 +5376,7 @@
         <v>46</v>
       </c>
       <c r="D111" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E111" t="s">
         <v>47</v>
@@ -5408,10 +5414,10 @@
         <v>51</v>
       </c>
       <c r="C112" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D112" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E112" t="s">
         <v>50</v>
@@ -5452,13 +5458,13 @@
         <v>52</v>
       </c>
       <c r="D113" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E113" t="s">
         <v>53</v>
       </c>
       <c r="F113" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G113" t="s">
         <v>18</v>
@@ -5490,10 +5496,10 @@
         <v>66</v>
       </c>
       <c r="C114" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D114" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E114" t="s">
         <v>96</v>
@@ -5528,16 +5534,16 @@
         <v>45</v>
       </c>
       <c r="C115" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D115" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E115" t="s">
         <v>111</v>
       </c>
       <c r="F115" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G115" t="s">
         <v>24</v>
@@ -5572,7 +5578,7 @@
         <v>43</v>
       </c>
       <c r="D116" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E116" t="s">
         <v>44</v>
@@ -5613,7 +5619,7 @@
         <v>55</v>
       </c>
       <c r="D117" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E117" t="s">
         <v>56</v>
@@ -5651,7 +5657,7 @@
         <v>57</v>
       </c>
       <c r="D118" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E118" t="s">
         <v>56</v>
@@ -5689,7 +5695,7 @@
         <v>36</v>
       </c>
       <c r="D119" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="E119" t="s">
         <v>37</v>
@@ -5730,13 +5736,13 @@
         <v>62</v>
       </c>
       <c r="D120" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E120" t="s">
         <v>31</v>
       </c>
       <c r="F120" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G120" t="s">
         <v>24</v>
@@ -5771,7 +5777,7 @@
         <v>71</v>
       </c>
       <c r="D121" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E121" t="s">
         <v>37</v>
@@ -5812,13 +5818,13 @@
         <v>77</v>
       </c>
       <c r="D122" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E122" t="s">
         <v>50</v>
       </c>
       <c r="F122" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G122" t="s">
         <v>18</v>
@@ -5850,16 +5856,16 @@
         <v>74</v>
       </c>
       <c r="C123" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D123" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E123" t="s">
         <v>117</v>
       </c>
       <c r="F123" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G123" t="s">
         <v>24</v>
@@ -5894,7 +5900,7 @@
         <v>67</v>
       </c>
       <c r="D124" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E124" t="s">
         <v>34</v>
@@ -5929,7 +5935,7 @@
         <v>79</v>
       </c>
       <c r="C125" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D125" t="s">
         <v>16</v>
@@ -6043,7 +6049,7 @@
         <v>87</v>
       </c>
       <c r="C128" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D128" t="s">
         <v>16</v>
@@ -6081,7 +6087,7 @@
         <v>84</v>
       </c>
       <c r="C129" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D129" t="s">
         <v>16</v>
@@ -6119,16 +6125,16 @@
         <v>94</v>
       </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E130" t="s">
         <v>41</v>
       </c>
       <c r="F130" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G130" t="s">
         <v>18</v>
@@ -6163,7 +6169,7 @@
         <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E131" t="s">
         <v>44</v>
@@ -6204,7 +6210,7 @@
         <v>75</v>
       </c>
       <c r="D132" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E132" t="s">
         <v>44</v>
@@ -6245,7 +6251,7 @@
         <v>47</v>
       </c>
       <c r="D133" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E133" t="s">
         <v>47</v>
@@ -6280,10 +6286,10 @@
         <v>100</v>
       </c>
       <c r="C134" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D134" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E134" t="s">
         <v>50</v>
@@ -6324,13 +6330,13 @@
         <v>82</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E135" t="s">
         <v>53</v>
       </c>
       <c r="F135" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G135" t="s">
         <v>18</v>
@@ -6365,7 +6371,7 @@
         <v>85</v>
       </c>
       <c r="D136" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E136" t="s">
         <v>53</v>
@@ -6406,7 +6412,7 @@
         <v>88</v>
       </c>
       <c r="D137" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E137" t="s">
         <v>89</v>
@@ -6444,16 +6450,16 @@
         <v>103</v>
       </c>
       <c r="C138" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D138" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E138" t="s">
         <v>93</v>
       </c>
       <c r="F138" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G138" t="s">
         <v>24</v>
@@ -6488,7 +6494,7 @@
         <v>91</v>
       </c>
       <c r="D139" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E139" t="s">
         <v>89</v>
@@ -6529,7 +6535,7 @@
         <v>93</v>
       </c>
       <c r="D140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E140" t="s">
         <v>93</v>
@@ -6564,7 +6570,7 @@
         <v>115</v>
       </c>
       <c r="C141" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D141" t="s">
         <v>16</v>
@@ -6573,7 +6579,7 @@
         <v>117</v>
       </c>
       <c r="F141" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G141" t="s">
         <v>24</v>
@@ -6605,7 +6611,7 @@
         <v>118</v>
       </c>
       <c r="C142" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D142" t="s">
         <v>16</v>
@@ -6754,19 +6760,19 @@
         <v>46188</v>
       </c>
       <c r="B146" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C146" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D146" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E146" t="s">
         <v>111</v>
       </c>
       <c r="F146" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G146" t="s">
         <v>24</v>
@@ -6798,7 +6804,7 @@
         <v>124</v>
       </c>
       <c r="C147" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D147" t="s">
         <v>16</v>
@@ -6833,10 +6839,10 @@
         <v>46195</v>
       </c>
       <c r="B148" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C148" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D148" t="s">
         <v>22</v>
@@ -6912,7 +6918,7 @@
         <v>46213</v>
       </c>
       <c r="B150" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C150" t="s">
         <v>110</v>
@@ -6924,7 +6930,7 @@
         <v>111</v>
       </c>
       <c r="F150" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G150" t="s">
         <v>24</v>
@@ -6953,10 +6959,10 @@
         <v>46221</v>
       </c>
       <c r="B151" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C151" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D151" t="s">
         <v>22</v>
@@ -6991,10 +6997,10 @@
         <v>46273</v>
       </c>
       <c r="B152" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C152" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D152" t="s">
         <v>16</v>
@@ -7029,10 +7035,10 @@
         <v>46277</v>
       </c>
       <c r="B153" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C153" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D153" t="s">
         <v>16</v>
@@ -7067,10 +7073,10 @@
         <v>46280</v>
       </c>
       <c r="B154" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C154" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D154" t="s">
         <v>16</v>
@@ -7105,13 +7111,13 @@
         <v>46283</v>
       </c>
       <c r="B155" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C155" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D155" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E155" t="s">
         <v>34</v>
@@ -7143,10 +7149,10 @@
         <v>46287</v>
       </c>
       <c r="B156" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C156" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D156" t="s">
         <v>16</v>
@@ -7155,7 +7161,7 @@
         <v>117</v>
       </c>
       <c r="F156" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G156" t="s">
         <v>24</v>
@@ -7184,10 +7190,10 @@
         <v>46291</v>
       </c>
       <c r="B157" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C157" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D157" t="s">
         <v>16</v>
@@ -7222,10 +7228,10 @@
         <v>46295</v>
       </c>
       <c r="B158" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C158" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D158" t="s">
         <v>16</v>
@@ -7234,7 +7240,7 @@
         <v>117</v>
       </c>
       <c r="F158" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G158" t="s">
         <v>24</v>
@@ -7300,7 +7306,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>4</v>
@@ -7312,24 +7318,24 @@
         <v>10</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -7346,13 +7352,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -7369,16 +7375,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4" s="4">
         <v>250</v>
@@ -7392,13 +7398,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -7413,18 +7419,18 @@
         <v>46273</v>
       </c>
       <c r="H5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -7439,18 +7445,18 @@
         <v>46291</v>
       </c>
       <c r="H6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -7462,18 +7468,18 @@
         <v>46286</v>
       </c>
       <c r="H7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -7485,7 +7491,7 @@
         <v>46289</v>
       </c>
       <c r="H8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -7516,7 +7522,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>8</v>
@@ -7528,12 +7534,12 @@
         <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -7542,7 +7548,7 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E2" s="4">
         <v>2400</v>
@@ -7550,7 +7556,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -7567,7 +7573,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -7576,7 +7582,7 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E4" s="4">
         <v>5800</v>
@@ -7584,7 +7590,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -7601,7 +7607,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -7615,7 +7621,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -7624,7 +7630,7 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E7" s="4">
         <v>2500</v>
@@ -7632,7 +7638,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -7641,7 +7647,7 @@
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E8" s="4">
         <v>1500</v>
@@ -7649,7 +7655,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -7658,7 +7664,7 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E9" s="4">
         <v>500</v>
@@ -7666,7 +7672,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -7683,7 +7689,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
@@ -7700,7 +7706,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -7717,7 +7723,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -7734,7 +7740,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -7748,7 +7754,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -7762,7 +7768,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
@@ -7771,7 +7777,7 @@
         <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E16" s="4">
         <v>400</v>
@@ -7779,7 +7785,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
@@ -7793,7 +7799,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -7810,7 +7816,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -7819,7 +7825,7 @@
         <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E19" s="4">
         <v>185</v>
@@ -7827,7 +7833,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -7836,7 +7842,7 @@
         <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E20" s="4">
         <v>650</v>
@@ -7844,7 +7850,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -7853,7 +7859,7 @@
         <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E21" s="4">
         <v>200</v>
@@ -7861,7 +7867,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
         <v>18</v>
@@ -7875,7 +7881,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
@@ -7889,7 +7895,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
@@ -7903,7 +7909,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s">
         <v>18</v>
@@ -7917,7 +7923,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
@@ -7931,7 +7937,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
@@ -7945,7 +7951,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
@@ -7959,7 +7965,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s">
         <v>18</v>
@@ -7973,7 +7979,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B30" t="s">
         <v>24</v>
@@ -7987,7 +7993,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
@@ -8001,7 +8007,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -8015,7 +8021,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -8029,7 +8035,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -8043,7 +8049,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -8057,7 +8063,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -8071,7 +8077,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -8085,7 +8091,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -8099,7 +8105,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -8113,7 +8119,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -8166,13 +8172,13 @@
         <v>8</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,13 +8186,13 @@
         <v>46142</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F2" s="4">
         <v>2400</v>
@@ -8197,13 +8203,13 @@
         <v>46142</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F3" s="4">
         <v>380</v>
@@ -8214,13 +8220,13 @@
         <v>46142</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F4" s="4">
         <v>150</v>
@@ -8256,10 +8262,10 @@
         <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8273,7 +8279,7 @@
         <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8287,7 +8293,7 @@
         <v>1908.6</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8301,7 +8307,7 @@
         <v>185.4</v>
       </c>
       <c r="D4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -8315,7 +8321,7 @@
         <v>3912.75</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8329,7 +8335,7 @@
         <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8343,7 +8349,7 @@
         <v>5991.55</v>
       </c>
       <c r="D7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8357,7 +8363,7 @@
         <v>258.3</v>
       </c>
       <c r="D8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8371,7 +8377,7 @@
         <v>13219.75</v>
       </c>
       <c r="D9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -8385,7 +8391,7 @@
         <v>579</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -8399,7 +8405,7 @@
         <v>13265.05</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -8465,10 +8471,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -8491,10 +8497,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -8517,19 +8523,19 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="J4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
@@ -8543,16 +8549,16 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
         <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="J5" t="s">
         <v>83</v>
@@ -8569,7 +8575,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E6" t="s">
         <v>80</v>
@@ -8578,7 +8584,7 @@
         <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -8589,7 +8595,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
         <v>49</v>
@@ -8598,10 +8604,10 @@
         <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -8609,16 +8615,19 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -8626,13 +8635,16 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E9" t="s">
         <v>85</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -8643,10 +8655,10 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F10" t="s">
         <v>34</v>
@@ -8660,10 +8672,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F11" t="s">
         <v>114</v>
@@ -8677,7 +8689,7 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
         <v>73</v>
@@ -8694,7 +8706,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E13" t="s">
         <v>75</v>
@@ -8711,7 +8723,7 @@
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
         <v>88</v>
@@ -8728,7 +8740,7 @@
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
         <v>91</v>
@@ -8745,7 +8757,7 @@
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
         <v>46</v>
@@ -8762,10 +8774,10 @@
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F17" t="s">
         <v>93</v>
@@ -8779,10 +8791,10 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E18" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
         <v>93</v>
@@ -8796,10 +8808,10 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
@@ -8813,7 +8825,7 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
@@ -8827,10 +8839,10 @@
         <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E21" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
         <v>117</v>
@@ -8838,7 +8850,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F22" t="s">
         <v>117</v>
@@ -8854,7 +8866,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
         <v>111</v>
@@ -8862,7 +8874,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s">
         <v>111</v>

--- a/fixtures/generated/tesouraria.xlsx
+++ b/fixtures/generated/tesouraria.xlsx
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="319">
   <si>
     <t>Tesouraria fictícia do TUNADÃO 1998</t>
   </si>
@@ -1022,7 +1022,16 @@
     <t>Valores, pendentes e acessos conferidos pelas duas direções e pelo Conselho Fiscal.</t>
   </si>
   <si>
+    <t>Marta Figueiredo</t>
+  </si>
+  <si>
+    <t>Duarte Pinheiro</t>
+  </si>
+  <si>
     <t>Conselho Fiscal</t>
+  </si>
+  <si>
+    <t>Helena Quintela</t>
   </si>
   <si>
     <t>Fim de ano letivo</t>
@@ -1998,19 +2007,25 @@
       <c r="A54" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="B54" s="11"/>
+      <c r="B54" s="11" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="B55" s="11"/>
+      <c r="B55" s="11" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="B56" s="11"/>
+        <v>300</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>301</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2038,7 +2053,7 @@
         <v>242</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2051,16 +2066,16 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B5" s="13">
         <v>46265</v>
@@ -2072,18 +2087,18 @@
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="14" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2096,7 +2111,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2135,7 +2150,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B19" s="11"/>
     </row>
@@ -2171,7 +2186,7 @@
         <v>242</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2184,7 +2199,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B4" s="12">
         <v>2025</v>
@@ -2198,28 +2213,28 @@
         <v>22</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2244,7 +2259,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2277,7 +2292,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B24" s="11"/>
     </row>
@@ -2289,7 +2304,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B26" s="11"/>
     </row>
